--- a/output/laminas_comunales/comunal_p_basica_a_2020_tarapaca.xlsx
+++ b/output/laminas_comunales/comunal_p_basica_a_2020_tarapaca.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C127"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -384,82 +384,1882 @@
         </is>
       </c>
       <c r="C2">
-        <v>53.76884460449219</v>
+        <v>146159.828125</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1404</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Huara</t>
+          <t>Camiña</t>
         </is>
       </c>
       <c r="C3">
-        <v>33.33333206176758</v>
+        <v>141292.34375</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1401</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pozo Almonte</t>
+          <t>Camiña</t>
         </is>
       </c>
       <c r="C4">
-        <v>18.27715301513672</v>
+        <v>136625.9375</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1107</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Alto Hospicio</t>
+          <t>Camiña</t>
         </is>
       </c>
       <c r="C5">
-        <v>17.68088150024414</v>
+        <v>136258.75</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1405</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Pica</t>
+          <t>Camiña</t>
         </is>
       </c>
       <c r="C6">
-        <v>17.20047378540039</v>
+        <v>135010.59375</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>131081.046875</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>126691.9921875</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>123928.703125</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>119285.640625</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>118942.421875</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>118309.59375</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>117300.2265625</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>117087.90625</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>116998.890625</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>116802.2578125</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>116619.8125</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>116565.765625</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>116392.96875</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>116040.40625</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>113650.6328125</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>113338.75</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>112930.0625</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>112708.828125</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>112350.65625</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>111951.28125</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>1101</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Iquique</t>
         </is>
       </c>
-      <c r="C7">
+      <c r="C27">
+        <v>111841.2421875</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>111684.7890625</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>110425.703125</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>109922.9140625</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>109912.7265625</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>108514.015625</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>107420.9375</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>106859.8984375</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>106646.9765625</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>106108.21875</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>104603.921875</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>104334.6640625</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>104181.796875</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>102850.2578125</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>101803.9453125</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>99660.40625</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>99050.0703125</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>74.07407379150391</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>72.85713958740234</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>63.72549057006836</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>61.42941665649414</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>57.27534484863281</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>56.12522125244141</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>55.28701019287109</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>55.1020393371582</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>54.97766494750977</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>54.54545593261719</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>53.94736862182617</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>53.76884460449219</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>53.57143020629883</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>53.50966262817383</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>52.92055892944336</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>52.8301887512207</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>52.51007843017578</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>52.44519424438477</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>51.5</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>51.16279220581055</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>51.1363639831543</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>50.78651809692383</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>50.47169876098633</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>50.27322387695313</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>49.46091461181641</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>49.20634841918945</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>49.17647171020508</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>48.79518127441406</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>46.70568466186523</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>46.37404632568359</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>45.90163803100586</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>45.43297576904297</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>44.36985778808594</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>43.97188186645508</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>43.29896926879883</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>43.29896926879883</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>42.94854736328125</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>42.77108383178711</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>42.34234237670898</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>42.08357620239258</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>41.62679290771484</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>39.77272796630859</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C86">
+        <v>39.40520477294922</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C87">
+        <v>37.73584747314453</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C88">
+        <v>37.57861709594727</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C89">
+        <v>36.75122833251953</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C90">
+        <v>36.68341827392578</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C91">
+        <v>34.42623138427734</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C92">
+        <v>33.33333206176758</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C93">
+        <v>32.65306091308594</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C94">
+        <v>30.39215660095215</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C95">
+        <v>30.15872955322266</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C96">
+        <v>28.33052253723145</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C97">
+        <v>27.27272796630859</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C98">
+        <v>27.13178253173828</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C99">
+        <v>26.60697174072266</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C100">
+        <v>26.05140113830566</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C101">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C102">
+        <v>24.7747745513916</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C103">
+        <v>24.56140327453613</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C104">
+        <v>23.80467987060547</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C105">
+        <v>20.71428489685059</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C106">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C107">
+        <v>18.5714282989502</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C108">
+        <v>18.51851844787598</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C109">
+        <v>18.27715301513672</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C110">
+        <v>17.68088150024414</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C111">
+        <v>17.66095733642578</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C112">
+        <v>17.20047378540039</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C113">
+        <v>16.16220664978027</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C114">
+        <v>15.72913932800293</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C115">
+        <v>15.10574054718018</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C116">
+        <v>14.35406684875488</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C117">
+        <v>12.26765823364258</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C118">
+        <v>12.26415061950684</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C119">
+        <v>12.21307945251465</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C120">
+        <v>12.09234142303467</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C121">
+        <v>11.91564178466797</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C122">
         <v>11.44354343414307</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C123">
+        <v>11.06870269775391</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C124">
+        <v>10.24258804321289</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C125">
+        <v>8.774728775024414</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C126">
+        <v>8.369617462158203</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C127">
+        <v>5.999806880950928</v>
       </c>
     </row>
   </sheetData>
